--- a/examples/pms/invoice.xlsx
+++ b/examples/pms/invoice.xlsx
@@ -67,7 +67,7 @@
     <xdr:ext cx="914400" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1" descr="{{image:logo}}"/>
+        <xdr:cNvPr id="1" name="Picture 1" descr="{d.logo}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -93,7 +93,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="4" width="20" customWidth="1"/>
@@ -102,7 +102,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>{{hotel}}</t>
+          <t>{d.hotel}</t>
         </is>
       </c>
     </row>
@@ -114,7 +114,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{{invoiceNumber}}</t>
+          <t>{d.invoiceNumber}</t>
         </is>
       </c>
     </row>
@@ -126,7 +126,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{{guest}}</t>
+          <t>{d.guest}</t>
         </is>
       </c>
     </row>
@@ -138,7 +138,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{{room}}</t>
+          <t>{d.room}</t>
         </is>
       </c>
     </row>
@@ -150,7 +150,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{{arrival}}</t>
+          <t>{d.arrival}</t>
         </is>
       </c>
     </row>
@@ -162,7 +162,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{{departure}}</t>
+          <t>{d.departure}</t>
         </is>
       </c>
     </row>
@@ -174,7 +174,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{{currency}}</t>
+          <t>{d.currency}</t>
         </is>
       </c>
     </row>
@@ -203,36 +203,38 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>{{#each items}}{{description}}</t>
+          <t>{d.items[i].description}</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{{quantity}}</t>
+          <t>{d.items[i].quantity}</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{{price}}</t>
+          <t>{d.items[i].price}</t>
         </is>
       </c>
       <c r="D11">
         <f>B11*C11</f>
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>{{/each}}</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>{d.items[i+1].description}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D12">
+      <c r="D13">
         <f>SUM(D11:D11)</f>
         <v>0</v>
       </c>

--- a/examples/pms/invoice.xlsx
+++ b/examples/pms/invoice.xlsx
@@ -59,12 +59,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="914400" cy="609600"/>
+    <xdr:ext cx="1645920" cy="548640"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1" descr="{d.logo}"/>
@@ -79,7 +79,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="914400" cy="609600"/>
+          <a:ext cx="1645920" cy="548640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -93,10 +93,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="4" width="20" customWidth="1"/>
+    <col min="2" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -235,11 +239,14 @@
         </is>
       </c>
       <c r="D13">
-        <f>SUM(D11:D11)</f>
+        <f>SUM(D10:D12)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <drawing r:id="rId70"/>
 </worksheet>
 </file>
